--- a/samples/financial_Model.xlsx
+++ b/samples/financial_Model.xlsx
@@ -523,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <cols>
     <col min="1" max="1" width="42.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -615,21 +615,38 @@
         <v>21.0641</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Total as % of target revenue</v>
+      </c>
+      <c r="B7" s="2">
+        <f>B6/Inputs!$B$4</f>
+        <v>0.05921338797814208</v>
+      </c>
+      <c r="C7" s="2">
+        <f>C6/Inputs!$B$4</f>
+        <v>0.08715887978142077</v>
+      </c>
+      <c r="D7" s="2">
+        <f>D6/Inputs!$B$4</f>
+        <v>0.11510437158469945</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>All cells on this sheet are formulas driven by the Inputs sheet.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -723,9 +740,47 @@
         <v>34.3</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Revenue growth (%)</v>
+      </c>
+      <c r="C6" s="2">
+        <f>(C2-B2)/B2</f>
+        <v>0.08450704225352124</v>
+      </c>
+      <c r="D6" s="2">
+        <f>(D2-C2)/C2</f>
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="E6" s="2">
+        <f>(E2-D2)/D2</f>
+        <v>0.08928571428571419</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>EBITDA margin (%)</v>
+      </c>
+      <c r="B7" s="2">
+        <f>B5/B2</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="C7" s="2">
+        <f>C5/C2</f>
+        <v>0.16103896103896106</v>
+      </c>
+      <c r="D7" s="2">
+        <f>D5/D2</f>
+        <v>0.17261904761904762</v>
+      </c>
+      <c r="E7" s="2">
+        <f>E5/E2</f>
+        <v>0.18743169398907103</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/financial_Model.xlsx
+++ b/samples/financial_Model.xlsx
@@ -4,8 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
-    <sheet name="Synergy Model" sheetId="2" r:id="rId2"/>
-    <sheet name="Historicals" sheetId="3" r:id="rId3"/>
+    <sheet name="Model" sheetId="2" r:id="rId2"/>
+    <sheet name="Synergies" sheetId="3" r:id="rId3"/>
+    <sheet name="Valuation" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -33,30 +34,236 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="#,##0.0;(#,##0.0)"/>
-    <numFmt numFmtId="61" formatCode="0.0%"/>
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <numFmts count="8">
+    <numFmt numFmtId="165" formatCode="#,##0.0;(#,##0.0)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0)"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0)"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0;(#,##0.0)"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0;(#,##0.0)"/>
+    <numFmt numFmtId="172" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="1">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
+  <fonts count="21" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="0A1F2E"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <i/>
+      <color rgb="63666A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="1A1A1A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="1F4E79"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="1F4E79"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="1F4E79"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="1F4E79"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="0A1F2E"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="0A1F2E"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="1A1A1A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="1A1A1A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="1A1A1A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="1A1A1A"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <i/>
+      <color rgb="63666A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="1A1A1A"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
+  <fills count="16">
+    <fill>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0A1F2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0A1F2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0A1F2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0A1F2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F7"/>
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -64,16 +271,162 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="D9D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="D9D9DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="D9D9DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D9D9DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="D9D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="D9D9DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="D9D9DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D9D9DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="D9D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="D9D9DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="D9D9DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D9D9DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="D9D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="D9D9DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="D9D9DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="D9D9DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0A1F2E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0A1F2E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0A1F2E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0A1F2E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="17" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="18" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -403,127 +756,471 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B24"/>
   <cols>
-    <col min="1" max="1" width="58.83203125" customWidth="1"/>
+    <col min="1" max="1" width="48.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Meridian Components Inc.: synergy model inputs ($M)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Client data (target), FY24A</v>
+      <c r="A1" s="3" t="str">
+        <v>Meridian Components Inc.: model inputs ($ millions)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="str">
+        <v>Yellow cells are inputs. Every other number in this workbook is a live formula linked to them.</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="5" t="str">
+        <v>CLIENT DATA, LATEST ACTUAL YEAR FY24A</v>
+      </c>
+      <c r="B4" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="str">
         <v>Revenue</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="8">
         <v>183</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
+    <row r="6">
+      <c r="A6" s="7" t="str">
         <v>Cost of goods sold</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="9">
         <v>114.9</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
+    <row r="7">
+      <c r="A7" s="7" t="str">
         <v>Opex / G&amp;A (back office)</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="9">
         <v>33.8</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Revenue synergy assumptions (INPUTS: change these, the model recalculates)</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="6" t="str">
+        <v>PROJECTION ASSUMPTIONS</v>
+      </c>
+      <c r="B9" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="str">
+        <v>Revenue growth, annual</v>
+      </c>
+      <c r="B10" s="10">
+        <v>0.08823055346886433</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="str">
+        <v>EBITDA margin, projection years</v>
+      </c>
+      <c r="B11" s="10">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="str">
+        <v>SYNERGY ASSUMPTIONS, EACH APPLIED TO ITS OWN LINE</v>
+      </c>
+      <c r="B13" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="str">
         <v>Revenue uplift, low end</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B14" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
+    <row r="15">
+      <c r="A15" s="7" t="str">
         <v>Revenue uplift, high end</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B15" s="10">
         <v>0.1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
+    <row r="16">
+      <c r="A16" s="7" t="str">
         <v>Flow through margin on new revenue</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B16" s="10">
         <v>0.187</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Cost synergy assumptions, each applied to its own cost line only (INPUTS)</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
+    <row r="17">
+      <c r="A17" s="7" t="str">
         <v>Cost of goods sold: synergy %, low end</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B17" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
+    <row r="18">
+      <c r="A18" s="7" t="str">
         <v>Cost of goods sold: synergy %, high end</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B18" s="10">
         <v>0.08</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
+    <row r="19">
+      <c r="A19" s="7" t="str">
         <v>Opex / G&amp;A (back office): synergy %, low end</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B19" s="10">
         <v>0.1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
+    <row r="20">
+      <c r="A20" s="7" t="str">
         <v>Opex / G&amp;A (back office): synergy %, high end</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B20" s="10">
         <v>0.25</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Conservative = low end of every range. Aggressive = high end. Midpoint = average.</v>
+    <row r="22">
+      <c r="A22" s="6" t="str">
+        <v>VALUATION ASSUMPTIONS</v>
+      </c>
+      <c r="B22" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="str">
+        <v>EV to EBITDA multiple</v>
+      </c>
+      <c r="B23" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="str">
+        <v>EV to revenue multiple, cross check</v>
+      </c>
+      <c r="B24" s="11">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:J9"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="str">
+        <v>Meridian Components Inc.: historicals and five year projection ($ millions)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="str">
+        <v>A = actual, F = forecast. Forecast cells are formulas driven by the Inputs sheet.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="str">
+        <v/>
+      </c>
+      <c r="B3" s="12" t="str">
+        <v>FY21A</v>
+      </c>
+      <c r="C3" s="13" t="str">
+        <v>FY22A</v>
+      </c>
+      <c r="D3" s="13" t="str">
+        <v>FY23A</v>
+      </c>
+      <c r="E3" s="13" t="str">
+        <v>FY24A</v>
+      </c>
+      <c r="F3" s="14" t="str">
+        <v>FY25F</v>
+      </c>
+      <c r="G3" s="15" t="str">
+        <v>FY26F</v>
+      </c>
+      <c r="H3" s="15" t="str">
+        <v>FY27F</v>
+      </c>
+      <c r="I3" s="15" t="str">
+        <v>FY28F</v>
+      </c>
+      <c r="J3" s="15" t="str">
+        <v>FY29F</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="str">
+        <v>Revenue</v>
+      </c>
+      <c r="B4" s="16">
+        <v>142</v>
+      </c>
+      <c r="C4" s="16">
+        <v>154</v>
+      </c>
+      <c r="D4" s="16">
+        <v>168</v>
+      </c>
+      <c r="E4" s="16">
+        <v>183</v>
+      </c>
+      <c r="F4" s="16">
+        <f>E4*(1+Inputs!$B$10)</f>
+        <v>199.14619128480217</v>
+      </c>
+      <c r="G4" s="16">
+        <f>F4*(1+Inputs!$B$10)</f>
+        <v>216.7169699630766</v>
+      </c>
+      <c r="H4" s="16">
+        <f>G4*(1+Inputs!$B$10)</f>
+        <v>235.83802816901408</v>
+      </c>
+      <c r="I4" s="16">
+        <f>H4*(1+Inputs!$B$10)</f>
+        <v>256.6461479233718</v>
+      </c>
+      <c r="J4" s="16">
+        <f>I4*(1+Inputs!$B$10)</f>
+        <v>279.2901796003029</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="B5" s="16">
+        <v>92.3</v>
+      </c>
+      <c r="C5" s="16">
+        <v>99.1</v>
+      </c>
+      <c r="D5" s="16">
+        <v>107</v>
+      </c>
+      <c r="E5" s="16">
+        <v>114.9</v>
+      </c>
+      <c r="F5" s="16">
+        <f>F4*(E5/E4)</f>
+        <v>125.03769059357252</v>
+      </c>
+      <c r="G5" s="16">
+        <f>G4*(E5/E4)</f>
+        <v>136.06983523911205</v>
+      </c>
+      <c r="H5" s="16">
+        <f>H4*(E5/E4)</f>
+        <v>148.0753521126761</v>
+      </c>
+      <c r="I5" s="16">
+        <f>I4*(E5/E4)</f>
+        <v>161.14012238467444</v>
+      </c>
+      <c r="J5" s="16">
+        <f>J4*(E5/E4)</f>
+        <v>175.35760456871483</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="str">
+        <v>Opex / SG&amp;A</v>
+      </c>
+      <c r="B6" s="16">
+        <v>28.4</v>
+      </c>
+      <c r="C6" s="16">
+        <v>30.1</v>
+      </c>
+      <c r="D6" s="16">
+        <v>32</v>
+      </c>
+      <c r="E6" s="16">
+        <v>33.8</v>
+      </c>
+      <c r="F6" s="16">
+        <f>F4*(E6/E4)</f>
+        <v>36.78219270724761</v>
+      </c>
+      <c r="G6" s="16">
+        <f>G4*(E6/E4)</f>
+        <v>40.02750592760649</v>
+      </c>
+      <c r="H6" s="16">
+        <f>H4*(E6/E4)</f>
+        <v>43.55915492957747</v>
+      </c>
+      <c r="I6" s="16">
+        <f>I4*(E6/E4)</f>
+        <v>47.402403277650095</v>
+      </c>
+      <c r="J6" s="16">
+        <f>J4*(E6/E4)</f>
+        <v>51.584743554591476</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="str">
+        <v>EBITDA</v>
+      </c>
+      <c r="B7" s="18">
+        <f>B4-B5-B6</f>
+        <v>21.300000000000004</v>
+      </c>
+      <c r="C7" s="19">
+        <f>C4-C5-C6</f>
+        <v>24.800000000000004</v>
+      </c>
+      <c r="D7" s="19">
+        <f>D4-D5-D6</f>
+        <v>29</v>
+      </c>
+      <c r="E7" s="19">
+        <f>E4-E5-E6</f>
+        <v>34.3</v>
+      </c>
+      <c r="F7" s="19">
+        <f>F4-F5-F6</f>
+        <v>37.32630798398204</v>
+      </c>
+      <c r="G7" s="19">
+        <f>G4-G5-G6</f>
+        <v>40.619628796358064</v>
+      </c>
+      <c r="H7" s="19">
+        <f>H4-H5-H6</f>
+        <v>44.20352112676056</v>
+      </c>
+      <c r="I7" s="19">
+        <f>I4-I5-I6</f>
+        <v>48.103622261047285</v>
+      </c>
+      <c r="J7" s="19">
+        <f>J4-J5-J6</f>
+        <v>52.34783147699667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="str">
+        <v>Revenue growth %</v>
+      </c>
+      <c r="C8" s="20">
+        <f>(C4-B4)/B4</f>
+        <v>0.08450704225352124</v>
+      </c>
+      <c r="D8" s="20">
+        <f>(D4-C4)/C4</f>
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="E8" s="20">
+        <f>(E4-D4)/D4</f>
+        <v>0.08928571428571419</v>
+      </c>
+      <c r="F8" s="20">
+        <f>(F4-E4)/E4</f>
+        <v>0.08823055346886433</v>
+      </c>
+      <c r="G8" s="20">
+        <f>(G4-F4)/F4</f>
+        <v>0.08823055346886433</v>
+      </c>
+      <c r="H8" s="20">
+        <f>(H4-G4)/G4</f>
+        <v>0.08823055346886433</v>
+      </c>
+      <c r="I8" s="20">
+        <f>(I4-H4)/H4</f>
+        <v>0.08823055346886433</v>
+      </c>
+      <c r="J8" s="20">
+        <f>(J4-I4)/I4</f>
+        <v>0.08823055346886433</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="str">
+        <v>EBITDA margin %</v>
+      </c>
+      <c r="B9" s="20">
+        <f>B7/B4</f>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="C9" s="20">
+        <f>C7/C4</f>
+        <v>0.16103896103896106</v>
+      </c>
+      <c r="D9" s="20">
+        <f>D7/D4</f>
+        <v>0.17261904761904762</v>
+      </c>
+      <c r="E9" s="20">
+        <f>E7/E4</f>
+        <v>0.18743169398907103</v>
+      </c>
+      <c r="F9" s="20">
+        <f>F7/F4</f>
+        <v>0.187431693989071</v>
+      </c>
+      <c r="G9" s="20">
+        <f>G7/G4</f>
+        <v>0.187431693989071</v>
+      </c>
+      <c r="H9" s="20">
+        <f>H7/H4</f>
+        <v>0.18743169398907103</v>
+      </c>
+      <c r="I9" s="20">
+        <f>I7/I4</f>
+        <v>0.18743169398907103</v>
+      </c>
+      <c r="J9" s="20">
+        <f>J7/J4</f>
+        <v>0.187431693989071</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D8"/>
   <cols>
     <col min="1" max="1" width="42.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -532,255 +1229,230 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Meridian Components Inc.: directional synergy model ($M, annual EBIT impact)</v>
+      <c r="A1" s="3" t="str">
+        <v>Meridian Components Inc.: annual synergy value scenarios ($ millions)</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="str">
+      <c r="A2" s="4" t="str">
+        <v>Conservative = low end of every range. Aggressive = high end. Midpoint = average.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="str">
+        <v/>
+      </c>
+      <c r="B3" s="13" t="str">
         <v>Conservative</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" s="13" t="str">
         <v>Midpoint</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D3" s="13" t="str">
         <v>Aggressive</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Revenue synergy (at flow through margin)</v>
-      </c>
-      <c r="B3" s="1">
-        <f>Inputs!$B$4*Inputs!$B$9*Inputs!$B$11</f>
+    <row r="4">
+      <c r="A4" s="7" t="str">
+        <v>Revenue synergy, at flow through margin</v>
+      </c>
+      <c r="B4" s="16">
+        <f>Inputs!$B$5*Inputs!$B$14*Inputs!$B$16</f>
         <v>1.71105</v>
       </c>
-      <c r="C3" s="1">
-        <f>Inputs!$B$4*AVERAGE(Inputs!$B$9,Inputs!$B$10)*Inputs!$B$11</f>
+      <c r="C4" s="16">
+        <f>Inputs!$B$5*AVERAGE(Inputs!$B$14,Inputs!$B$15)*Inputs!$B$16</f>
         <v>2.5665750000000003</v>
       </c>
-      <c r="D3" s="1">
-        <f>Inputs!$B$4*Inputs!$B$10*Inputs!$B$11</f>
+      <c r="D4" s="16">
+        <f>Inputs!$B$5*Inputs!$B$15*Inputs!$B$16</f>
         <v>3.4221</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
+    <row r="5">
+      <c r="A5" s="7" t="str">
         <v>Cost of goods sold synergy</v>
       </c>
-      <c r="B4" s="1">
-        <f>Inputs!$B$5*Inputs!$B$14</f>
+      <c r="B5" s="16">
+        <f>Inputs!$B$6*Inputs!$B$17</f>
         <v>5.745000000000001</v>
       </c>
-      <c r="C4" s="1">
-        <f>Inputs!$B$5*AVERAGE(Inputs!$B$14,Inputs!$B$15)</f>
+      <c r="C5" s="16">
+        <f>Inputs!$B$6*AVERAGE(Inputs!$B$17,Inputs!$B$18)</f>
         <v>7.468500000000001</v>
       </c>
-      <c r="D4" s="1">
-        <f>Inputs!$B$5*Inputs!$B$15</f>
+      <c r="D5" s="16">
+        <f>Inputs!$B$6*Inputs!$B$18</f>
         <v>9.192</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
+    <row r="6">
+      <c r="A6" s="7" t="str">
         <v>Opex / G&amp;A (back office) synergy</v>
       </c>
-      <c r="B5" s="1">
-        <f>Inputs!$B$6*Inputs!$B$16</f>
+      <c r="B6" s="16">
+        <f>Inputs!$B$7*Inputs!$B$19</f>
         <v>3.38</v>
       </c>
-      <c r="C5" s="1">
-        <f>Inputs!$B$6*AVERAGE(Inputs!$B$16,Inputs!$B$17)</f>
+      <c r="C6" s="16">
+        <f>Inputs!$B$7*AVERAGE(Inputs!$B$19,Inputs!$B$20)</f>
         <v>5.914999999999999</v>
       </c>
-      <c r="D5" s="1">
-        <f>Inputs!$B$6*Inputs!$B$17</f>
+      <c r="D6" s="16">
+        <f>Inputs!$B$7*Inputs!$B$20</f>
         <v>8.45</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
+    <row r="7">
+      <c r="A7" s="21" t="str">
         <v>Total synergy value</v>
       </c>
-      <c r="B6" s="1">
-        <f>SUM(B3:B5)</f>
+      <c r="B7" s="19">
+        <f>SUM(B4:B6)</f>
         <v>10.83605</v>
       </c>
-      <c r="C6" s="1">
-        <f>SUM(C3:C5)</f>
+      <c r="C7" s="19">
+        <f>SUM(C4:C6)</f>
         <v>15.950075</v>
       </c>
-      <c r="D6" s="1">
-        <f>SUM(D3:D5)</f>
+      <c r="D7" s="19">
+        <f>SUM(D4:D6)</f>
         <v>21.0641</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Total as % of target revenue</v>
-      </c>
-      <c r="B7" s="2">
-        <f>B6/Inputs!$B$4</f>
+    <row r="8">
+      <c r="A8" s="7" t="str">
+        <v>Total as % of revenue</v>
+      </c>
+      <c r="B8" s="20">
+        <f>B7/Inputs!$B$5</f>
         <v>0.05921338797814208</v>
       </c>
-      <c r="C7" s="2">
-        <f>C6/Inputs!$B$4</f>
+      <c r="C8" s="20">
+        <f>C7/Inputs!$B$5</f>
         <v>0.08715887978142077</v>
       </c>
-      <c r="D7" s="2">
-        <f>D6/Inputs!$B$4</f>
+      <c r="D8" s="20">
+        <f>D7/Inputs!$B$5</f>
         <v>0.11510437158469945</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>All cells on this sheet are formulas driven by the Inputs sheet.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:B14"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="46.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Historical financials ($M)</v>
-      </c>
-      <c r="B1" t="str">
-        <v>FY21A</v>
-      </c>
-      <c r="C1" t="str">
-        <v>FY22A</v>
-      </c>
-      <c r="D1" t="str">
-        <v>FY23A</v>
-      </c>
-      <c r="E1" t="str">
-        <v>FY24A</v>
+      <c r="A1" s="3" t="str">
+        <v>Meridian Components Inc.: valuation view ($ millions)</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Revenue</v>
-      </c>
-      <c r="B2" s="1">
-        <v>142</v>
-      </c>
-      <c r="C2" s="1">
-        <v>154</v>
-      </c>
-      <c r="D2" s="1">
-        <v>168</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="A2" s="4" t="str">
+        <v>Change the multiples on the Inputs sheet; every value here recalculates.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="str">
+        <v>ENTERPRISE VALUE AT THE EV TO EBITDA MULTIPLE</v>
+      </c>
+      <c r="B4" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="str">
+        <v>EBITDA, FY24A actual</v>
+      </c>
+      <c r="B5" s="16">
+        <f>Model!E7</f>
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="str">
+        <v>Enterprise value at the multiple</v>
+      </c>
+      <c r="B6" s="16">
+        <f>B5*Inputs!$B$23</f>
+        <v>274.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="str">
+        <v>Midpoint annual synergy value</v>
+      </c>
+      <c r="B7" s="16">
+        <f>Synergies!C7</f>
+        <v>15.950075</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="str">
+        <v>EBITDA including synergy capture</v>
+      </c>
+      <c r="B8" s="16">
+        <f>B5+B7</f>
+        <v>50.250074999999995</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="str">
+        <v>Enterprise value including synergy capture</v>
+      </c>
+      <c r="B9" s="16">
+        <f>B8*Inputs!$B$23</f>
+        <v>402.00059999999996</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="str">
+        <v>Value creation from synergy capture</v>
+      </c>
+      <c r="B10" s="19">
+        <f>B9-B6</f>
+        <v>127.6006</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="str">
+        <v>REVENUE CROSS CHECK</v>
+      </c>
+      <c r="B12" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="str">
+        <v>Revenue, FY24A actual</v>
+      </c>
+      <c r="B13" s="16">
+        <f>Inputs!$B$5</f>
         <v>183</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>COGS</v>
-      </c>
-      <c r="B3" s="1">
-        <v>92.3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>99.1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>107</v>
-      </c>
-      <c r="E3" s="1">
-        <v>114.9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Opex</v>
-      </c>
-      <c r="B4" s="1">
-        <v>28.4</v>
-      </c>
-      <c r="C4" s="1">
-        <v>30.1</v>
-      </c>
-      <c r="D4" s="1">
-        <v>32</v>
-      </c>
-      <c r="E4" s="1">
-        <v>33.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>EBITDA</v>
-      </c>
-      <c r="B5" s="1">
-        <v>21.300000000000004</v>
-      </c>
-      <c r="C5" s="1">
-        <v>24.800000000000004</v>
-      </c>
-      <c r="D5" s="1">
-        <v>29</v>
-      </c>
-      <c r="E5" s="1">
-        <v>34.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Revenue growth (%)</v>
-      </c>
-      <c r="C6" s="2">
-        <f>(C2-B2)/B2</f>
-        <v>0.08450704225352124</v>
-      </c>
-      <c r="D6" s="2">
-        <f>(D2-C2)/C2</f>
-        <v>0.09090909090909083</v>
-      </c>
-      <c r="E6" s="2">
-        <f>(E2-D2)/D2</f>
-        <v>0.08928571428571419</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>EBITDA margin (%)</v>
-      </c>
-      <c r="B7" s="2">
-        <f>B5/B2</f>
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="C7" s="2">
-        <f>C5/C2</f>
-        <v>0.16103896103896106</v>
-      </c>
-      <c r="D7" s="2">
-        <f>D5/D2</f>
-        <v>0.17261904761904762</v>
-      </c>
-      <c r="E7" s="2">
-        <f>E5/E2</f>
-        <v>0.18743169398907103</v>
+    <row r="14">
+      <c r="A14" s="7" t="str">
+        <v>Enterprise value at the revenue multiple</v>
+      </c>
+      <c r="B14" s="16">
+        <f>B13*Inputs!$B$24</f>
+        <v>274.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/financial_Model.xlsx
+++ b/samples/financial_Model.xlsx
@@ -35,7 +35,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="8">
+  <numFmts count="10">
     <numFmt numFmtId="165" formatCode="#,##0.0;(#,##0.0)"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0)"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
@@ -44,8 +44,10 @@
     <numFmt numFmtId="170" formatCode="#,##0.0;(#,##0.0)"/>
     <numFmt numFmtId="171" formatCode="#,##0.0;(#,##0.0)"/>
     <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="173" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="174" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -166,8 +168,20 @@
       <b/>
       <color rgb="1A1A1A"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+      <color rgb="0A1F2E"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -259,6 +273,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F5F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0A1F2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -378,7 +404,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -425,6 +451,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="21" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="22" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1346,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F23"/>
   <cols>
     <col min="1" max="1" width="46.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1450,9 +1482,189 @@
         <v>274.5</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="str">
+        <v>SENSITIVITY: EV ON NEXT YEAR EBITDA, ACROSS GROWTH AND MULTIPLE</v>
+      </c>
+      <c r="B16" s="6" t="str">
+        <v/>
+      </c>
+      <c r="C16" s="6" t="str">
+        <v/>
+      </c>
+      <c r="D16" s="6" t="str">
+        <v/>
+      </c>
+      <c r="E16" s="6" t="str">
+        <v/>
+      </c>
+      <c r="F16" s="6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="str">
+        <v>Growth below, multiple right</v>
+      </c>
+      <c r="B17" s="22">
+        <f>Inputs!$B$23+-2</f>
+        <v>6</v>
+      </c>
+      <c r="C17" s="22">
+        <f>Inputs!$B$23+-1</f>
+        <v>7</v>
+      </c>
+      <c r="D17" s="22">
+        <f>Inputs!$B$23+0</f>
+        <v>8</v>
+      </c>
+      <c r="E17" s="22">
+        <f>Inputs!$B$23+1</f>
+        <v>9</v>
+      </c>
+      <c r="F17" s="22">
+        <f>Inputs!$B$23+2</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23">
+        <f>Inputs!$B$10+-0.02</f>
+        <v>0.06823055346886432</v>
+      </c>
+      <c r="B18" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <v>219.8418479038923</v>
+      </c>
+      <c r="C18" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <v>256.48215588787434</v>
+      </c>
+      <c r="D18" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <v>293.1224638718564</v>
+      </c>
+      <c r="E18" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <v>329.7627718558384</v>
+      </c>
+      <c r="F18" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <v>366.40307983982046</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23">
+        <f>Inputs!$B$10+-0.01</f>
+        <v>0.07823055346886433</v>
+      </c>
+      <c r="B19" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <v>221.89984790389227</v>
+      </c>
+      <c r="C19" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <v>258.8831558878743</v>
+      </c>
+      <c r="D19" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <v>295.86646387185635</v>
+      </c>
+      <c r="E19" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <v>332.8497718558384</v>
+      </c>
+      <c r="F19" s="16">
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <v>369.83307983982047</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23">
+        <f>Inputs!$B$10+0</f>
+        <v>0.08823055346886433</v>
+      </c>
+      <c r="B20" s="16">
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <v>223.9578479038923</v>
+      </c>
+      <c r="C20" s="16">
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <v>261.28415588787436</v>
+      </c>
+      <c r="D20" s="19">
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <v>298.6104638718564</v>
+      </c>
+      <c r="E20" s="16">
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <v>335.9367718558384</v>
+      </c>
+      <c r="F20" s="16">
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <v>373.2630798398205</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23">
+        <f>Inputs!$B$10+0.01</f>
+        <v>0.09823055346886432</v>
+      </c>
+      <c r="B21" s="16">
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <v>226.01584790389228</v>
+      </c>
+      <c r="C21" s="16">
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <v>263.6851558878743</v>
+      </c>
+      <c r="D21" s="16">
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <v>301.35446387185635</v>
+      </c>
+      <c r="E21" s="16">
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <v>339.0237718558384</v>
+      </c>
+      <c r="F21" s="16">
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <v>376.6930798398204</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23">
+        <f>Inputs!$B$10+0.02</f>
+        <v>0.10823055346886433</v>
+      </c>
+      <c r="B22" s="16">
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <v>228.07384790389224</v>
+      </c>
+      <c r="C22" s="16">
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <v>266.08615588787427</v>
+      </c>
+      <c r="D22" s="16">
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <v>304.0984638718563</v>
+      </c>
+      <c r="E22" s="16">
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <v>342.1107718558384</v>
+      </c>
+      <c r="F22" s="16">
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <v>380.12307983982043</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="str">
+        <v>EBITDA in each cell is next year revenue at that growth times the current margin.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/financial_Model.xlsx
+++ b/samples/financial_Model.xlsx
@@ -788,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <cols>
     <col min="1" max="1" width="48.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -852,105 +852,97 @@
         <v>0.08823055346886433</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="str">
-        <v>EBITDA margin, projection years</v>
-      </c>
-      <c r="B11" s="10">
-        <v>0.187</v>
+    <row r="12">
+      <c r="A12" s="6" t="str">
+        <v>SYNERGY ASSUMPTIONS, EACH APPLIED TO ITS OWN LINE</v>
+      </c>
+      <c r="B12" s="6" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="str">
-        <v>SYNERGY ASSUMPTIONS, EACH APPLIED TO ITS OWN LINE</v>
-      </c>
-      <c r="B13" s="6" t="str">
-        <v/>
+      <c r="A13" s="7" t="str">
+        <v>Revenue uplift, low end</v>
+      </c>
+      <c r="B13" s="10">
+        <v>0.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="str">
-        <v>Revenue uplift, low end</v>
+        <v>Revenue uplift, high end</v>
       </c>
       <c r="B14" s="10">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="str">
-        <v>Revenue uplift, high end</v>
+        <v>Flow through margin on new revenue</v>
       </c>
       <c r="B15" s="10">
-        <v>0.1</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="str">
-        <v>Flow through margin on new revenue</v>
+        <v>Cost of goods sold: synergy %, low end</v>
       </c>
       <c r="B16" s="10">
-        <v>0.187</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="str">
-        <v>Cost of goods sold: synergy %, low end</v>
+        <v>Cost of goods sold: synergy %, high end</v>
       </c>
       <c r="B17" s="10">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="str">
-        <v>Cost of goods sold: synergy %, high end</v>
+        <v>Opex / G&amp;A (back office): synergy %, low end</v>
       </c>
       <c r="B18" s="10">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="str">
-        <v>Opex / G&amp;A (back office): synergy %, low end</v>
+        <v>Opex / G&amp;A (back office): synergy %, high end</v>
       </c>
       <c r="B19" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="str">
-        <v>Opex / G&amp;A (back office): synergy %, high end</v>
-      </c>
-      <c r="B20" s="10">
         <v>0.25</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="6" t="str">
+        <v>VALUATION ASSUMPTIONS</v>
+      </c>
+      <c r="B21" s="6" t="str">
+        <v/>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="6" t="str">
-        <v>VALUATION ASSUMPTIONS</v>
-      </c>
-      <c r="B22" s="6" t="str">
-        <v/>
+      <c r="A22" s="7" t="str">
+        <v>EV to EBITDA multiple</v>
+      </c>
+      <c r="B22" s="11">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="str">
-        <v>EV to EBITDA multiple</v>
+        <v>EV to revenue multiple, cross check</v>
       </c>
       <c r="B23" s="11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="str">
-        <v>EV to revenue multiple, cross check</v>
-      </c>
-      <c r="B24" s="11">
         <v>1.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1289,15 +1281,15 @@
         <v>Revenue synergy, at flow through margin</v>
       </c>
       <c r="B4" s="16">
-        <f>Inputs!$B$5*Inputs!$B$14*Inputs!$B$16</f>
+        <f>Inputs!$B$5*Inputs!$B$13*Inputs!$B$15</f>
         <v>1.71105</v>
       </c>
       <c r="C4" s="16">
-        <f>Inputs!$B$5*AVERAGE(Inputs!$B$14,Inputs!$B$15)*Inputs!$B$16</f>
+        <f>Inputs!$B$5*AVERAGE(Inputs!$B$13,Inputs!$B$14)*Inputs!$B$15</f>
         <v>2.5665750000000003</v>
       </c>
       <c r="D4" s="16">
-        <f>Inputs!$B$5*Inputs!$B$15*Inputs!$B$16</f>
+        <f>Inputs!$B$5*Inputs!$B$14*Inputs!$B$15</f>
         <v>3.4221</v>
       </c>
     </row>
@@ -1306,15 +1298,15 @@
         <v>Cost of goods sold synergy</v>
       </c>
       <c r="B5" s="16">
+        <f>Inputs!$B$6*Inputs!$B$16</f>
+        <v>5.745000000000001</v>
+      </c>
+      <c r="C5" s="16">
+        <f>Inputs!$B$6*AVERAGE(Inputs!$B$16,Inputs!$B$17)</f>
+        <v>7.468500000000001</v>
+      </c>
+      <c r="D5" s="16">
         <f>Inputs!$B$6*Inputs!$B$17</f>
-        <v>5.745000000000001</v>
-      </c>
-      <c r="C5" s="16">
-        <f>Inputs!$B$6*AVERAGE(Inputs!$B$17,Inputs!$B$18)</f>
-        <v>7.468500000000001</v>
-      </c>
-      <c r="D5" s="16">
-        <f>Inputs!$B$6*Inputs!$B$18</f>
         <v>9.192</v>
       </c>
     </row>
@@ -1323,15 +1315,15 @@
         <v>Opex / G&amp;A (back office) synergy</v>
       </c>
       <c r="B6" s="16">
+        <f>Inputs!$B$7*Inputs!$B$18</f>
+        <v>3.38</v>
+      </c>
+      <c r="C6" s="16">
+        <f>Inputs!$B$7*AVERAGE(Inputs!$B$18,Inputs!$B$19)</f>
+        <v>5.914999999999999</v>
+      </c>
+      <c r="D6" s="16">
         <f>Inputs!$B$7*Inputs!$B$19</f>
-        <v>3.38</v>
-      </c>
-      <c r="C6" s="16">
-        <f>Inputs!$B$7*AVERAGE(Inputs!$B$19,Inputs!$B$20)</f>
-        <v>5.914999999999999</v>
-      </c>
-      <c r="D6" s="16">
-        <f>Inputs!$B$7*Inputs!$B$20</f>
         <v>8.45</v>
       </c>
     </row>
@@ -1416,7 +1408,7 @@
         <v>Enterprise value at the multiple</v>
       </c>
       <c r="B6" s="16">
-        <f>B5*Inputs!$B$23</f>
+        <f>B5*Inputs!$B$22</f>
         <v>274.4</v>
       </c>
     </row>
@@ -1443,7 +1435,7 @@
         <v>Enterprise value including synergy capture</v>
       </c>
       <c r="B9" s="16">
-        <f>B8*Inputs!$B$23</f>
+        <f>B8*Inputs!$B$22</f>
         <v>402.00059999999996</v>
       </c>
     </row>
@@ -1478,7 +1470,7 @@
         <v>Enterprise value at the revenue multiple</v>
       </c>
       <c r="B14" s="16">
-        <f>B13*Inputs!$B$24</f>
+        <f>B13*Inputs!$B$23</f>
         <v>274.5</v>
       </c>
     </row>
@@ -1507,23 +1499,23 @@
         <v>Growth below, multiple right</v>
       </c>
       <c r="B17" s="22">
-        <f>Inputs!$B$23+-2</f>
+        <f>Inputs!$B$22+-2</f>
         <v>6</v>
       </c>
       <c r="C17" s="22">
-        <f>Inputs!$B$23+-1</f>
+        <f>Inputs!$B$22+-1</f>
         <v>7</v>
       </c>
       <c r="D17" s="22">
-        <f>Inputs!$B$23+0</f>
+        <f>Inputs!$B$22+0</f>
         <v>8</v>
       </c>
       <c r="E17" s="22">
-        <f>Inputs!$B$23+1</f>
+        <f>Inputs!$B$22+1</f>
         <v>9</v>
       </c>
       <c r="F17" s="22">
-        <f>Inputs!$B$23+2</f>
+        <f>Inputs!$B$22+2</f>
         <v>10</v>
       </c>
     </row>
@@ -1533,23 +1525,23 @@
         <v>0.06823055346886432</v>
       </c>
       <c r="B18" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$22+-2)</f>
         <v>219.8418479038923</v>
       </c>
       <c r="C18" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$22+-1)</f>
         <v>256.48215588787434</v>
       </c>
       <c r="D18" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$22+0)</f>
         <v>293.1224638718564</v>
       </c>
       <c r="E18" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$22+1)</f>
         <v>329.7627718558384</v>
       </c>
       <c r="F18" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <f>B13*(1+Inputs!$B$10+-0.02)*(B5/B13)*(Inputs!$B$22+2)</f>
         <v>366.40307983982046</v>
       </c>
     </row>
@@ -1559,23 +1551,23 @@
         <v>0.07823055346886433</v>
       </c>
       <c r="B19" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$22+-2)</f>
         <v>221.89984790389227</v>
       </c>
       <c r="C19" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$22+-1)</f>
         <v>258.8831558878743</v>
       </c>
       <c r="D19" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$22+0)</f>
         <v>295.86646387185635</v>
       </c>
       <c r="E19" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$22+1)</f>
         <v>332.8497718558384</v>
       </c>
       <c r="F19" s="16">
-        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <f>B13*(1+Inputs!$B$10+-0.01)*(B5/B13)*(Inputs!$B$22+2)</f>
         <v>369.83307983982047</v>
       </c>
     </row>
@@ -1585,23 +1577,23 @@
         <v>0.08823055346886433</v>
       </c>
       <c r="B20" s="16">
-        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$22+-2)</f>
         <v>223.9578479038923</v>
       </c>
       <c r="C20" s="16">
-        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$22+-1)</f>
         <v>261.28415588787436</v>
       </c>
       <c r="D20" s="19">
-        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$22+0)</f>
         <v>298.6104638718564</v>
       </c>
       <c r="E20" s="16">
-        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$22+1)</f>
         <v>335.9367718558384</v>
       </c>
       <c r="F20" s="16">
-        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <f>B13*(1+Inputs!$B$10+0)*(B5/B13)*(Inputs!$B$22+2)</f>
         <v>373.2630798398205</v>
       </c>
     </row>
@@ -1611,23 +1603,23 @@
         <v>0.09823055346886432</v>
       </c>
       <c r="B21" s="16">
-        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$22+-2)</f>
         <v>226.01584790389228</v>
       </c>
       <c r="C21" s="16">
-        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$22+-1)</f>
         <v>263.6851558878743</v>
       </c>
       <c r="D21" s="16">
-        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$22+0)</f>
         <v>301.35446387185635</v>
       </c>
       <c r="E21" s="16">
-        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$22+1)</f>
         <v>339.0237718558384</v>
       </c>
       <c r="F21" s="16">
-        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <f>B13*(1+Inputs!$B$10+0.01)*(B5/B13)*(Inputs!$B$22+2)</f>
         <v>376.6930798398204</v>
       </c>
     </row>
@@ -1637,23 +1629,23 @@
         <v>0.10823055346886433</v>
       </c>
       <c r="B22" s="16">
-        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+-2)</f>
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$22+-2)</f>
         <v>228.07384790389224</v>
       </c>
       <c r="C22" s="16">
-        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+-1)</f>
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$22+-1)</f>
         <v>266.08615588787427</v>
       </c>
       <c r="D22" s="16">
-        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+0)</f>
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$22+0)</f>
         <v>304.0984638718563</v>
       </c>
       <c r="E22" s="16">
-        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+1)</f>
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$22+1)</f>
         <v>342.1107718558384</v>
       </c>
       <c r="F22" s="16">
-        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$23+2)</f>
+        <f>B13*(1+Inputs!$B$10+0.02)*(B5/B13)*(Inputs!$B$22+2)</f>
         <v>380.12307983982043</v>
       </c>
     </row>

--- a/samples/financial_Model.xlsx
+++ b/samples/financial_Model.xlsx
@@ -58,7 +58,7 @@
     </font>
     <font>
       <sz val="13"/>
-      <name val="Arial"/>
+      <name val="Georgia"/>
       <b/>
       <color rgb="0A1F2E"/>
     </font>
